--- a/data/S1964_65_FINAL.xlsx
+++ b/data/S1964_65_FINAL.xlsx
@@ -26,8 +26,11 @@
     <sheet name="SERIES" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="CLUBS" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="META" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$17</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +80,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,12 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -18132,7 +18150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18181,6 +18199,223 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1964_65_0002 'Sparta ČKD Praha' ROZBITÝ prev CLUB_S1963_64_0062 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1964_65_0034 'ČKD Praha' prev→CLUB_S1963_64_0047 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1964_65_0041 'TJ Gottwaldov B' ROZBITÝ prev CLUB_S1963_64_0546 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1964_65_0051 'Štart Nitra' prev→CLUB_S1963_64_0056 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1964_65_0056 'Bohemians ČKD Praha' ROZBITÝ prev CLUB_S1963_64_0062 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1964_65_0076 'ČKD Praha B' prev→CLUB_S1963_64_0047 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1964_65_0093 'Sparta Podluhy' ROZBITÝ prev CLUB_S1963_64_0085 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1964_65_0271 'RH Ostrov' prev→CLUB_S1963_64_0626 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1964_65_0307 'Slovan NV Ústí nad Labem' prev→CLUB_S1963_64_0051 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1964_65_0466 'Dynamo Jihlava' prev→CLUB_S1963_64_0055 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1964_65_0508 'Slatina B' ROZBITÝ prev CLUB_S1963_64_0762 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0012</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1964_65_0012 'KVAL  skupina A' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0013</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1964_65_0013 'KVAL  skupina B' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0014</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1964_65_0014 'KVAL  skupina C' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0015</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1964_65_0015 'KVAL  skupina D' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0105</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1964_65_0105 '30_SVK kvalifikace o KP' (L25, parent=NODE_S1964_65_0100) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -26528,10 +26763,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -32481,7 +32712,6 @@
         </is>
       </c>
     </row>
-    <row r="192"/>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
@@ -35121,7 +35351,6 @@
         </is>
       </c>
     </row>
-    <row r="250"/>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
@@ -37033,7 +37262,6 @@
         </is>
       </c>
     </row>
-    <row r="294"/>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
@@ -39328,7 +39556,6 @@
         </is>
       </c>
     </row>
-    <row r="347"/>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
@@ -43768,7 +43995,6 @@
         </is>
       </c>
     </row>
-    <row r="445"/>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
@@ -47482,7 +47708,6 @@
         </is>
       </c>
     </row>
-    <row r="530"/>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
@@ -51540,7 +51765,6 @@
         </is>
       </c>
     </row>
-    <row r="622"/>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
@@ -51901,7 +52125,6 @@
         </is>
       </c>
     </row>
-    <row r="633"/>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
@@ -52506,7 +52729,6 @@
         </is>
       </c>
     </row>
-    <row r="651"/>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
@@ -55669,6 +55891,413 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0002</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0002 'Sparta ČKD Praha' ROZBITÝ prev CLUB_S1963_64_0062 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0034</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0034 'ČKD Praha' prev→CLUB_S1963_64_0047 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0041</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0041 'TJ Gottwaldov B' ROZBITÝ prev CLUB_S1963_64_0546 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0051</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0051 'Štart Nitra' prev→CLUB_S1963_64_0056 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0056</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0056 'Bohemians ČKD Praha' ROZBITÝ prev CLUB_S1963_64_0062 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0076</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0076 'ČKD Praha B' prev→CLUB_S1963_64_0047 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0093</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0093 'Sparta Podluhy' ROZBITÝ prev CLUB_S1963_64_0085 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0271</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0271 'RH Ostrov' prev→CLUB_S1963_64_0626 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0307</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0307 'Slovan NV Ústí nad Labem' prev→CLUB_S1963_64_0051 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0466</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0466 'Dynamo Jihlava' prev→CLUB_S1963_64_0055 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0508</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0508 'Slatina B' ROZBITÝ prev CLUB_S1963_64_0762 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0012</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1964_65_0012 'KVAL  skupina A' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0013</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1964_65_0013 'KVAL  skupina B' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0014</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1964_65_0014 'KVAL  skupina C' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0015</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1964_65_0015 'KVAL  skupina D' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0105</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1964_65_0105 '30_SVK kvalifikace o KP' (L25, parent=NODE_S1964_65_0100) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F17"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1964_65_FINAL.xlsx
+++ b/data/S1964_65_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -877,7 +877,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>CLUB_S1963_64_0062</t>
+          <t>CLUB_S1963_64_0004</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -6806,11 +6806,7 @@
           <t>CLUB_S1964_65_0508</t>
         </is>
       </c>
-      <c r="R62" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1963_64_0762</t>
-        </is>
-      </c>
+      <c r="R62" s="3" t="n"/>
       <c r="S62" s="3" t="n"/>
       <c r="T62" s="3" t="n"/>
       <c r="U62" s="3" t="n"/>
@@ -8802,6 +8798,11 @@
           <t>CLUB_S1963_64_0659</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>setrval</t>
+        </is>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>TR_S1964_65_00306</t>
@@ -10338,6 +10339,11 @@
       <c r="T27" t="inlineStr">
         <is>
           <t>kvalifikace</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>postup</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -18150,7 +18156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18205,7 +18211,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1964_65_0002 'Sparta ČKD Praha' ROZBITÝ prev CLUB_S1963_64_0062 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0004 'Spartak Praha Sokolovo'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -18217,7 +18223,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1964_65_0034 'ČKD Praha' prev→CLUB_S1963_64_0047 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18229,7 +18235,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1964_65_0041 'TJ Gottwaldov B' ROZBITÝ prev CLUB_S1963_64_0546 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18241,7 +18247,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1964_65_0051 'Štart Nitra' prev→CLUB_S1963_64_0056 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0053 'TJ Gottwaldov B'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18253,7 +18259,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1964_65_0056 'Bohemians ČKD Praha' ROZBITÝ prev CLUB_S1963_64_0062 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0056 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18265,7 +18271,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1964_65_0076 'ČKD Praha B' prev→CLUB_S1963_64_0047 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -18277,7 +18283,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1964_65_0093 'Sparta Podluhy' ROZBITÝ prev CLUB_S1963_64_0085 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0047 'ČKD Praha'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -18289,7 +18295,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1964_65_0271 'RH Ostrov' prev→CLUB_S1963_64_0626 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -18301,7 +18307,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1964_65_0307 'Slovan NV Ústí nad Labem' prev→CLUB_S1963_64_0051 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18313,7 +18319,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1964_65_0466 'Dynamo Jihlava' prev→CLUB_S1963_64_0055 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Velké Popovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -18325,7 +18331,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1964_65_0508 'Slatina B' ROZBITÝ prev CLUB_S1963_64_0762 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -18335,14 +18341,9 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NODE_S1964_65_0012</t>
-        </is>
-      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1964_65_0012 'KVAL  skupina A' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0049 'Sokol Podluhy'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -18352,14 +18353,9 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NODE_S1964_65_0013</t>
-        </is>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1964_65_0013 'KVAL  skupina B' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -18369,14 +18365,9 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NODE_S1964_65_0014</t>
-        </is>
-      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1964_65_0014 'KVAL  skupina C' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -18386,14 +18377,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NODE_S1964_65_0015</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1964_65_0015 'KVAL  skupina D' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -18403,17 +18389,228 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NODE_S1964_65_0105</t>
-        </is>
-      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1964_65_0105 '30_SVK kvalifikace o KP' (L25, parent=NODE_S1964_65_0100) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0626 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0051 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lomnice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0055 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vír' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0756 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0469 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24590,12 +24787,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CLUB_S1963_64_0062</t>
+          <t>CLUB_S1963_64_0004</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha. || TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0004 'Spartak Praha Sokolovo'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -25645,12 +25842,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -26112,12 +26309,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CLUB_S1963_64_0546</t>
+          <t>CLUB_S1963_64_0053</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Jiskra Gottwaldov B (B-tým). clean: II → B. Oprava city: "I. Gottwaldov" → "Gottwaldov" (I. = předpona, ne město). || Gottwaldov = Zlín = RI Okna Berani Zlín / PSG Zlín (Wiki D42 - registr ustavy 04/2026). Mesto se 1949-1990 jmenovalo Gottwaldov! Hlavni chain: SK Zlín -&gt; Sokol Bata -&gt; Svit Gottwaldov (Svit = Bata) -&gt; Spartak Gottwaldov -&gt; TJ Gottwaldov -&gt; 1990 prejmenovani na PSG Zlín -&gt; Berani Zlín. I. Gottwaldov / II. Gottwaldov = skupiny tymu. city Zlín.</t>
+          <t>Jiskra Gottwaldov B (B-tým). clean: II → B. Oprava city: "I. Gottwaldov" → "Gottwaldov" (I. = předpona, ne město). || Gottwaldov = Zlín = RI Okna Berani Zlín / PSG Zlín (Wiki D42 - registr ustavy 04/2026). Mesto se 1949-1990 jmenovalo Gottwaldov! Hlavni chain: SK Zlín -&gt; Sokol Bata -&gt; Svit Gottwaldov (Svit = Bata) -&gt; Spartak Gottwaldov -&gt; TJ Gottwaldov -&gt; 1990 prejmenovani na PSG Zlín -&gt; Berani Zlín. I. Gottwaldov / II. Gottwaldov = skupiny tymu. city Zlín. || TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0053 'TJ Gottwaldov B'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -26537,12 +26734,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -26569,12 +26766,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CLUB_S1963_64_0062</t>
+          <t>CLUB_S1963_64_0047</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Po skonceni souteze zmena nazvu z TJ CKD Praha na TJ Bohemians CKD Praha. || Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha.</t>
+          <t>Po skonceni souteze zmena nazvu z TJ CKD Praha na TJ Bohemians CKD Praha. || Identity transition VERIFIKOVÁNA Wikipedií (D18) — genealogie: ZMP Praha → Sokol Šverma Jinonice → Spartak Motorlet Praha. Almanach 51/52 zachycuje fázi „Sokol Šverma Jinonice" s odkazem na předchůdce ZSJ ZMP Praha. (TBD odstraněn 04/2026.) || Šverma Jinonice (ZSJ ZMP Praha) 51/52 (10_liga, postup do 1.ligy). I. ČLTK Praha (Wiki D18 / D42). Genealogie: I. ČLTK Praha (1923, Český Lawn-tenisový klub) -&gt; Sokol ZMP Praha (1948) -&gt; ZSJ ZMP Praha (1949) -&gt; ZSJ Sokol Šverma Jinonice (1951) -&gt; DSO Spartak Motorlet Praha (1953) -&gt; TJ Spartak Motorlet Praha (1957) -&gt; TJ ČLTK Motorlet Praha (1969) -&gt; TJ DP I. ČLTK Praha (1970) -&gt; I. ČLTK Praha (1992). Motorlet = zavod ve čtvrti Jinonice (Praha 5). city Praha. || Praha = vsechny prazske kluby (Wiki D42 - registr ustavy 04/2026). VELKA metropole, VICE rovnocennych chains (D45 TYP 1). HLAVNI: (1) HC Sparta Praha (1903-) - dnes Tipsport ELH. (2) HC Slavia Praha (1900) - dnes 1.liga. (3) Skoda Plzen sice ne, ale prazsky paralelni: HC Kobra Praha. Mestske casti: Vokovice, Aritma, Strešovice, Strašnice, Tesla, Vyšehrad, Motol, Hostivař, Kobylisy, Vinohrady, Podolí, Dejvice, Holešovice, Vršovice, Bohnice, Karlín, Smíchov, Žižkov, Nuseľ, Libeň, Vysočany. Stalingrad = mestska cast Prahy 7 (1949-1962, dnes Holešovice). Železničáři Praha = paralelni Lokomotiva chain. city Praha. || TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0047 'ČKD Praha'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -26763,6 +26960,10 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -27557,12 +27758,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Velké Popovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -27599,12 +27800,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -27720,12 +27921,12 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>CLUB_S1963_64_0085</t>
+          <t>CLUB_S1963_64_0049</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Podluhy = Sparta/Sokol Podluhy (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). city Podluhy.</t>
+          <t>Podluhy = Sparta/Sokol Podluhy (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). city Podluhy. || TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0049 'Sokol Podluhy'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -32712,6 +32913,7 @@
         </is>
       </c>
     </row>
+    <row r="192"/>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
@@ -32965,12 +33167,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -33880,12 +34082,12 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -34016,12 +34218,12 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -34251,12 +34453,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou.</t>
+          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nad Lipou</t>
+          <t>Kamenice nad Lipou</t>
         </is>
       </c>
     </row>
@@ -35013,12 +35215,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice.</t>
+          <t>Hoštice (Wiki D42 - registr ustavy 04/2026). POZOR: vícero Hostic - Stredske Hoštice (Jihocesky, okres Strakonice), Sloupne Hoštice (Jihocesky), Male Hoštice (Severomoravsky, mestska cast Opavy). 'Slovan Male Hoštice' = Severomoravsky! 'Dukla Strelske Hostice' = vojensky Strelske Hostice u Strakonic. city Hoštice. || TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Slovan Malé Hoštice</t>
+          <t>Malé Hoštice</t>
         </is>
       </c>
     </row>
@@ -35351,6 +35553,7 @@
         </is>
       </c>
     </row>
+    <row r="250"/>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
@@ -37262,6 +37465,7 @@
         </is>
       </c>
     </row>
+    <row r="294"/>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
@@ -39556,6 +39760,7 @@
         </is>
       </c>
     </row>
+    <row r="347"/>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
@@ -40385,12 +40590,12 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Hradec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -40998,12 +41203,12 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi</t>
+          <t>Rosice u Chrasti</t>
         </is>
       </c>
     </row>
@@ -42831,12 +43036,12 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>Lomnice nL Popelkou = Slavoj/Jiskra Lomnice nL Popelkou (Wiki D42 - registr ustavy 04/2026). Liberecky kraj (okres Semily). city Lomnice nad Popelkou. POZOR: Vícero Lomnic v CR - Lomnice u Tisnova, Lomnice u Sokolova.</t>
+          <t>Lomnice nL Popelkou = Slavoj/Jiskra Lomnice nL Popelkou (Wiki D42 - registr ustavy 04/2026). Liberecky kraj (okres Semily). city Lomnice nad Popelkou. POZOR: Vícero Lomnic v CR - Lomnice u Tisnova, Lomnice u Sokolova. || TBD: city 'Lomnice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>Lomnice</t>
+          <t>Lomnice nad Popelkou</t>
         </is>
       </c>
     </row>
@@ -43316,12 +43521,12 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>Horní Staré Město = TJ Jiskra Horní Staré Město (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (mestska cast Trutnova!). NE Stare Mesto u UH (Jihomoravsky), NE Stare Mesto u Sumperka. city Trutnov (Horní Staré Město).</t>
+          <t>Horní Staré Město = TJ Jiskra Horní Staré Město (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (mestska cast Trutnova!). NE Stare Mesto u UH (Jihomoravsky), NE Stare Mesto u Sumperka. city Trutnov (Horní Staré Město). || TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>Horní Staré Město</t>
+          <t>Staré Město</t>
         </is>
       </c>
     </row>
@@ -43995,6 +44200,7 @@
         </is>
       </c>
     </row>
+    <row r="445"/>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
@@ -46196,14 +46402,9 @@
           <t>skupina B</t>
         </is>
       </c>
-      <c r="H496" t="inlineStr">
-        <is>
-          <t>CLUB_S1963_64_0762</t>
-        </is>
-      </c>
       <c r="I496" t="inlineStr">
         <is>
-          <t>Slatina = TJ Sokol/Dukla Slatina (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (mestska cast Brna - **Brno-Slatina!**). city Brno (Slatina).</t>
+          <t>Slatina = TJ Sokol/Dukla Slatina (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (mestska cast Brna - **Brno-Slatina!**). city Brno (Slatina). || TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J496" t="inlineStr">
@@ -47657,12 +47858,12 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>Vír = TJ Jiskra/Sokol Vír (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sázavou). Patterns: Sokol Vír -&gt; Jiskra Vír. city Vír.</t>
+          <t>Vír = TJ Jiskra/Sokol Vír (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sázavou). Patterns: Sokol Vír -&gt; Jiskra Vír. city Vír. || TBD: city 'Vír' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>Vír</t>
+          <t>Moravské Budějovice</t>
         </is>
       </c>
     </row>
@@ -47708,6 +47909,7 @@
         </is>
       </c>
     </row>
+    <row r="530"/>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
@@ -47951,12 +48153,12 @@
       </c>
       <c r="I536" t="inlineStr">
         <is>
-          <t>Orlová = TJ Banik Důl Zápotocký Orlová (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Důl Zápotocký** = OKD důl pojmenovany po Antoninu Zapotockem. city Orlová.</t>
+          <t>Orlová = TJ Banik Důl Zápotocký Orlová (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Důl Zápotocký** = OKD důl pojmenovany po Antoninu Zapotockem. city Orlová. || TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J536" t="inlineStr">
         <is>
-          <t>Důl Zápotocký Orlová</t>
+          <t>Orlová</t>
         </is>
       </c>
     </row>
@@ -51765,6 +51967,7 @@
         </is>
       </c>
     </row>
+    <row r="622"/>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
@@ -52125,6 +52328,7 @@
         </is>
       </c>
     </row>
+    <row r="633"/>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
@@ -52412,12 +52616,12 @@
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -52729,6 +52933,7 @@
         </is>
       </c>
     </row>
+    <row r="651"/>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
@@ -55050,7 +55255,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>CLUB_S1963_64_0546</t>
+          <t>CLUB_S1963_64_0053</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -55897,11 +56102,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -55946,7 +56151,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -55956,11 +56161,9 @@
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0002 'Sparta ČKD Praha' ROZBITÝ prev CLUB_S1963_64_0062 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0004 'Spartak Praha Sokolovo'; ověřit [fix_broken_prev_d42]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -55968,21 +56171,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0034</t>
+          <t>CLUB_S1964_65_0029</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0034 'ČKD Praha' prev→CLUB_S1963_64_0047 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -55990,21 +56191,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0041</t>
+          <t>CLUB_S1964_65_0034</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0041 'TJ Gottwaldov B' ROZBITÝ prev CLUB_S1963_64_0546 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -56012,21 +56211,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0051</t>
+          <t>CLUB_S1964_65_0041</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0051 'Štart Nitra' prev→CLUB_S1963_64_0056 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0053 'TJ Gottwaldov B'; ověřit [fix_broken_prev_d42]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -56034,21 +56231,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0056</t>
+          <t>CLUB_S1964_65_0051</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0056 'Bohemians ČKD Praha' ROZBITÝ prev CLUB_S1963_64_0062 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0056 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -56056,21 +56251,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0076</t>
+          <t>CLUB_S1964_65_0055</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0076 'ČKD Praha B' prev→CLUB_S1963_64_0047 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -56078,21 +56271,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0093</t>
+          <t>CLUB_S1964_65_0056</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0093 'Sparta Podluhy' ROZBITÝ prev CLUB_S1963_64_0085 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0047 'ČKD Praha'; ověřit [fix_broken_prev_d42]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -56100,21 +56291,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0271</t>
+          <t>CLUB_S1964_65_0065</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0271 'RH Ostrov' prev→CLUB_S1963_64_0626 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -56122,21 +56311,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0307</t>
+          <t>CLUB_S1964_65_0076</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0307 'Slovan NV Ústí nad Labem' prev→CLUB_S1963_64_0051 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -56144,21 +56331,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0466</t>
+          <t>CLUB_S1964_65_0089</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0466 'Dynamo Jihlava' prev→CLUB_S1963_64_0055 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: city 'Voděrady' → 'Velké Popovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -56166,21 +56351,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0508</t>
+          <t>CLUB_S1964_65_0090</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0508 'Slatina B' ROZBITÝ prev CLUB_S1963_64_0762 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -56188,21 +56371,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NODE_S1964_65_0012</t>
+          <t>CLUB_S1964_65_0093</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1964_65_0012 'KVAL  skupina A' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0049 'Sokol Podluhy'; ověřit [fix_broken_prev_d42]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -56210,21 +56391,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NODE_S1964_65_0013</t>
+          <t>CLUB_S1964_65_0210</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1964_65_0013 'KVAL  skupina B' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -56232,21 +56411,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NODE_S1964_65_0014</t>
+          <t>CLUB_S1964_65_0230</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1964_65_0014 'KVAL  skupina C' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -56254,21 +56431,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NODE_S1964_65_0015</t>
+          <t>CLUB_S1964_65_0233</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1964_65_0015 'KVAL  skupina D' (L25, parent=NODE_S1964_65_0011) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -56276,24 +56451,382 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NODE_S1964_65_0105</t>
+          <t>CLUB_S1964_65_0238</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1964_65_0105 '30_SVK kvalifikace o KP' (L25, parent=NODE_S1964_65_0100) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0254</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0271</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0626 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0307</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0051 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0369</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0378</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0392</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0431</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lomnice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0441</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0466</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0055 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0485</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0508</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0540</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vír' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0548</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0641</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0642</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0756 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0651</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0653</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1964_65_0665</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0469 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F17"/>
+  <autoFilter ref="A1:F35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -56920,7 +57453,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>CLUB_S1963_64_0062</t>
+          <t>CLUB_S1963_64_0047</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -60509,7 +61042,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>CLUB_S1963_64_0085</t>
+          <t>CLUB_S1963_64_0049</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">

--- a/data/S1964_65_FINAL.xlsx
+++ b/data/S1964_65_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18156,7 +18156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18223,7 +18223,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -18235,7 +18235,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0053 'TJ Gottwaldov B'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -18247,7 +18247,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0053 'TJ Gottwaldov B'; ověřit [fix_broken_prev_d42]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0056 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -18259,7 +18259,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0056 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -18271,7 +18271,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0047 'ČKD Praha'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -18283,7 +18283,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0047 'ČKD Praha'; ověřit [fix_broken_prev_d42]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -18295,7 +18295,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -18307,7 +18307,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Velké Popovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18319,7 +18319,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Velké Popovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -18331,7 +18331,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0049 'Sokol Podluhy'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -18343,7 +18343,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0049 'Sokol Podluhy'; ověřit [fix_broken_prev_d42]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -18355,7 +18355,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -18367,7 +18367,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -18379,7 +18379,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -18391,7 +18391,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -18403,7 +18403,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0626 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -18415,7 +18415,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0626 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0051 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -18427,7 +18427,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0051 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -18439,7 +18439,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lomnice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -18451,7 +18451,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -18463,7 +18463,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0055 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -18475,7 +18475,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lomnice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -18487,7 +18487,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -18499,7 +18499,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0055 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -18511,7 +18511,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -18523,7 +18523,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0756 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -18535,7 +18535,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vír' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -18547,7 +18547,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -18559,58 +18559,10 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0469 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0756 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0469 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -18627,7 +18579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18686,6 +18638,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18728,6 +18685,11 @@
           <t>12 týmů: základ → finále 1-6 + o 7-12 + kvalifikace o I.ligu (9.-10. + vítězové II.ligy). Mistr: ZKL Brno. Sestup: Ostrava, Motorlet. Od příští sezóny liga jen 10 týmů.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18775,6 +18737,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -18817,6 +18784,11 @@
           <t>4 skupiny po 8 (ctyrkolove). Posledni tymy skupin A-D sestoupily primo; predposledni tymy skupin A-C hraly o udrzeni v kvalifikaci o II.ligu. Kladno B ukoncilo cinnost -&gt; Trebic zustal.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18859,6 +18831,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18901,6 +18878,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18943,6 +18925,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18985,6 +18972,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -19027,6 +19019,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -19069,6 +19066,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -19111,6 +19113,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -19158,6 +19165,11 @@
           <t>Vitezove krajskych preboru. Ve skupine B Dvur Kralove n/L nenastoupil (kont. 0:5). Po 3. kole odstoupil Havirov-Sucha; dalsi neodehrana utkání kont. 0:5. Chybi vysledky tretin.</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -19200,6 +19212,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -19242,6 +19259,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -19284,6 +19306,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -19326,6 +19353,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -19368,6 +19400,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -19536,6 +19573,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0019</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -19578,6 +19620,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0020</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19620,6 +19667,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0021</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19662,6 +19714,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0022</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -19704,6 +19761,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0023</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -20087,6 +20149,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0031</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -20129,6 +20196,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0032</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -20171,6 +20243,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0033</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -20213,6 +20290,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0034</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -20255,6 +20337,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0035</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -20302,6 +20389,11 @@
           <t>Kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0036</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -20344,6 +20436,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0037</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -20685,6 +20782,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0045</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -20853,6 +20955,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0049</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -20895,6 +21002,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0050</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -20937,6 +21049,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0051</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -20979,6 +21096,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0052</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -21063,6 +21185,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0054</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -21105,6 +21232,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0055</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -21147,6 +21279,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0056</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -21189,6 +21326,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0057</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -21231,6 +21373,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0058</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -21273,6 +21420,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0059</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -21315,6 +21467,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0060</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -21357,6 +21514,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0061</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -21399,6 +21561,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0062</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -21441,6 +21608,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0064</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -21483,6 +21655,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0065</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -21525,6 +21702,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0066</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -21567,6 +21749,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0067</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -21661,6 +21848,11 @@
           <t>kvalifikace o KS</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0068</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -21703,6 +21895,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0069</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -21745,6 +21942,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0070</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -21787,6 +21989,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0071</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -21829,6 +22036,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0072</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -21871,6 +22083,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0073</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -22170,6 +22387,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0081</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -22212,6 +22434,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0082</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -22254,6 +22481,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0083</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -22296,6 +22528,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0084</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -22338,6 +22575,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0085</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -22763,6 +23005,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0095</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -22800,6 +23047,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0098</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -22919,6 +23171,11 @@
       <c r="J101" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1963_64_0102</t>
         </is>
       </c>
     </row>
@@ -25842,12 +26099,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -40590,12 +40847,12 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí. || TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Spartak Hradec Králové = Mountfield HK (Wiki D42 - registr ustavy 04/2026). Chain ZSJ Skoda HK -&gt; Spartak ZVU -&gt; Spartak HK -&gt; Stadion HK -&gt; Mountfield HK. city Hradec Králové. || Hradec nL Moravicí = Spartak/Brano Hradec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Opava). Brano = podnik. POZOR: NE Hradec Králové (Vychodocesky)! Brano Hradec Podolí = jine, k overeni Pavlem. city Hradec nad Moravicí.</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Hradec nad Moravicí</t>
         </is>
       </c>
     </row>
@@ -41203,12 +41460,12 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi. || TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Rosice u Chrudimi = TJ Dynamo Rosice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj (okres Chrudim, district 'okres Chrudim' potvrzen). 'B' = druzstvo B. POZOR: NE Rosice u Brna (Jihomoravsky)! city Rosice u Chrudimi.</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>Rosice u Chrasti</t>
+          <t>Rosice u Chrudimi</t>
         </is>
       </c>
     </row>
@@ -47858,12 +48115,12 @@
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>Vír = TJ Jiskra/Sokol Vír (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sázavou). Patterns: Sokol Vír -&gt; Jiskra Vír. city Vír. || TBD: city 'Vír' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Vír = TJ Jiskra/Sokol Vír (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj (okres Žďár nL Sázavou). Patterns: Sokol Vír -&gt; Jiskra Vír. city Vír.</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>Moravské Budějovice</t>
+          <t>Vír</t>
         </is>
       </c>
     </row>
@@ -56102,7 +56359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -56176,12 +56433,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0029</t>
+          <t>CLUB_S1964_65_0034</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56196,12 +56453,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0034</t>
+          <t>CLUB_S1964_65_0041</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0053 'TJ Gottwaldov B'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -56216,12 +56473,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0041</t>
+          <t>CLUB_S1964_65_0051</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0053 'TJ Gottwaldov B'; ověřit [fix_broken_prev_d42]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0056 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56236,12 +56493,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0051</t>
+          <t>CLUB_S1964_65_0055</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0056 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56256,12 +56513,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0055</t>
+          <t>CLUB_S1964_65_0056</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0047 'ČKD Praha'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -56276,12 +56533,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0056</t>
+          <t>CLUB_S1964_65_0065</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0047 'ČKD Praha'; ověřit [fix_broken_prev_d42]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56296,12 +56553,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0065</t>
+          <t>CLUB_S1964_65_0076</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56316,12 +56573,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0076</t>
+          <t>CLUB_S1964_65_0089</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Voděrady' → 'Velké Popovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56336,12 +56593,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0089</t>
+          <t>CLUB_S1964_65_0090</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Voděrady' → 'Velké Popovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56356,12 +56613,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0090</t>
+          <t>CLUB_S1964_65_0093</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0049 'Sokol Podluhy'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -56376,12 +56633,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0093</t>
+          <t>CLUB_S1964_65_0210</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0049 'Sokol Podluhy'; ověřit [fix_broken_prev_d42]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56396,12 +56653,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0210</t>
+          <t>CLUB_S1964_65_0230</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56416,12 +56673,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0230</t>
+          <t>CLUB_S1964_65_0233</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56436,12 +56693,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0233</t>
+          <t>CLUB_S1964_65_0238</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56456,12 +56713,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0238</t>
+          <t>CLUB_S1964_65_0254</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56476,12 +56733,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0254</t>
+          <t>CLUB_S1964_65_0271</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0626 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56496,12 +56753,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0271</t>
+          <t>CLUB_S1964_65_0307</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0626 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0051 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56516,12 +56773,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0307</t>
+          <t>CLUB_S1964_65_0369</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0051 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56536,12 +56793,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0369</t>
+          <t>CLUB_S1964_65_0431</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Lomnice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56556,12 +56813,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0378</t>
+          <t>CLUB_S1964_65_0441</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hradec' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56576,12 +56833,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0392</t>
+          <t>CLUB_S1964_65_0466</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rosice u Chrudimi' → 'Rosice u Chrasti' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0055 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56596,12 +56853,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0431</t>
+          <t>CLUB_S1964_65_0485</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lomnice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -56616,12 +56873,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0441</t>
+          <t>CLUB_S1964_65_0508</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -56636,12 +56893,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0466</t>
+          <t>CLUB_S1964_65_0548</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0055 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56656,12 +56913,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0485</t>
+          <t>CLUB_S1964_65_0641</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56676,12 +56933,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0508</t>
+          <t>CLUB_S1964_65_0642</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0756 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56696,12 +56953,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0540</t>
+          <t>CLUB_S1964_65_0651</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vír' → 'Moravské Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56716,12 +56973,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0548</t>
+          <t>CLUB_S1964_65_0653</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56736,97 +56993,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0641</t>
+          <t>CLUB_S1964_65_0665</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S1964_65_0642</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0756 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S1964_65_0651</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S1964_65_0653</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S1964_65_0665</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0469 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F35"/>
+  <autoFilter ref="A1:F31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1964_65_FINAL.xlsx
+++ b/data/S1964_65_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>I. A třída / skupina A / ŽD Pudlov — odstoupil</t>
+          <t>I. A třída / skupina A</t>
         </is>
       </c>
       <c r="C25" s="2" t="n"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>I. A třída / skupina A / ŽD Pudlov — odstoupil / skupina B</t>
+          <t>I. A třída / skupina A / skupina B</t>
         </is>
       </c>
       <c r="C26" s="2" t="n"/>
@@ -10755,7 +10755,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>I. A třída / skupina A / ŽD Pudlov — odstoupil / skupina C</t>
+          <t>I. A třída / skupina A / skupina C</t>
         </is>
       </c>
       <c r="C33" s="2" t="n"/>
@@ -11284,7 +11284,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>I. A třída / skupina A / ŽD Pudlov — odstoupil / skupina D</t>
+          <t>I. A třída / skupina A / skupina D</t>
         </is>
       </c>
       <c r="C40" s="2" t="n"/>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>I. A třída / skupina A / ŽD Pudlov — odstoupil / kvalifikace</t>
+          <t>I. A třída / skupina A / kvalifikace</t>
         </is>
       </c>
       <c r="C47" s="2" t="n"/>
@@ -18156,7 +18156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18209,81 +18209,131 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0004 'Spartak Praha Sokolovo'; ověřit [fix_broken_prev_d42]</t>
+          <t>[club-fate] TJ Stará Role — odstoupila (club_id: CLUB_S1964_65_0300)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[club-fate] ŽD Pudlov — odstoupil</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0089</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0053 'TJ Gottwaldov B'; ověřit [fix_broken_prev_d42]</t>
+          <t>[club-fate] ŽD Pudlov — odstoupil</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0090</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0056 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[club-fate] ŽD Pudlov — odstoupil</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0091</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[club-fate] ŽD Pudlov — odstoupil</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0092</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30SVMR</t>
+        </is>
+      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0047 'ČKD Praha'; ověřit [fix_broken_prev_d42]</t>
+          <t>[club-fate] ŽD Pudlov — odstoupil</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0004 'Spartak Praha Sokolovo'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -18307,7 +18357,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Velké Popovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0053 'TJ Gottwaldov B'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -18319,7 +18369,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0056 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -18331,7 +18381,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0049 'Sokol Podluhy'; ověřit [fix_broken_prev_d42]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -18343,7 +18393,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0047 'ČKD Praha'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -18355,7 +18405,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -18367,7 +18417,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0047 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -18379,7 +18429,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Velké Popovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -18391,7 +18441,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -18403,7 +18453,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0626 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id (D42/city) → CLUB_S1963_64_0049 'Sokol Podluhy'; ověřit [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -18415,7 +18465,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0051 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -18427,7 +18477,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -18439,7 +18489,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lomnice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -18451,7 +18501,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -18463,7 +18513,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0055 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovan Malé Hoštice' → 'Malé Hoštice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -18475,7 +18525,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0626 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -18487,7 +18537,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'TJ Stará Role — odstoupila' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -18499,7 +18549,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0051 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -18511,7 +18561,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -18523,7 +18573,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0756 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lomnice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -18535,7 +18585,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -18547,7 +18597,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0055 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -18559,10 +18609,94 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0756 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1963_64_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0469 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -37488,7 +37622,7 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Stará Role = TJ Stará Role (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (mestska cast Karlovych Varu). city Karlovy Vary.</t>
+          <t>Stará Role = TJ Stará Role (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (mestska cast Karlovych Varu). city Karlovy Vary. || TBD: extrahováno z block_name: 'TJ Stará Role — odstoupila' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
@@ -56359,7 +56493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -56753,12 +56887,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0307</t>
+          <t>CLUB_S1964_65_0300</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0051 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: extrahováno z block_name: 'TJ Stará Role — odstoupila' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -56773,12 +56907,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0369</t>
+          <t>CLUB_S1964_65_0307</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0051 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56793,12 +56927,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0431</t>
+          <t>CLUB_S1964_65_0369</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lomnice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0052 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56813,12 +56947,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0441</t>
+          <t>CLUB_S1964_65_0431</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lomnice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56833,12 +56967,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0466</t>
+          <t>CLUB_S1964_65_0441</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0055 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Horní Staré Město' → 'Staré Město' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56853,12 +56987,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0485</t>
+          <t>CLUB_S1964_65_0466</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0055 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56873,12 +57007,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0508</t>
+          <t>CLUB_S1964_65_0485</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -56893,12 +57027,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0548</t>
+          <t>CLUB_S1964_65_0508</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -56913,12 +57047,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0641</t>
+          <t>CLUB_S1964_65_0548</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Důl Zápotocký Orlová' → 'Orlová' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -56933,12 +57067,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0642</t>
+          <t>CLUB_S1964_65_0641</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0756 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0058 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56953,12 +57087,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0651</t>
+          <t>CLUB_S1964_65_0642</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0756 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56973,12 +57107,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1964_65_0653</t>
+          <t>CLUB_S1964_65_0651</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1963_64_0057 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -56993,17 +57127,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
+          <t>CLUB_S1964_65_0653</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>CLUB_S1964_65_0665</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>TBD: auto-prev_club_id doplnění → CLUB_S1963_64_0469 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F31"/>
+  <autoFilter ref="A1:F32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -74136,7 +74290,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>I.třída / skupina C / TJ Stará Role — odstoupila</t>
+          <t>I.třída / skupina C</t>
         </is>
       </c>
       <c r="C42" s="2" t="n"/>

--- a/data/S1964_65_FINAL.xlsx
+++ b/data/S1964_65_FINAL.xlsx
@@ -928,7 +928,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="M7" t="n">
         <v>33</v>
@@ -1232,7 +1232,7 @@
         <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>

--- a/data/S1964_65_FINAL.xlsx
+++ b/data/S1964_65_FINAL.xlsx
@@ -27351,10 +27351,6 @@
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -33304,7 +33300,6 @@
         </is>
       </c>
     </row>
-    <row r="192"/>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
@@ -35944,7 +35939,6 @@
         </is>
       </c>
     </row>
-    <row r="250"/>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
@@ -37856,7 +37850,6 @@
         </is>
       </c>
     </row>
-    <row r="294"/>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
@@ -40151,7 +40144,6 @@
         </is>
       </c>
     </row>
-    <row r="347"/>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
@@ -44591,7 +44583,6 @@
         </is>
       </c>
     </row>
-    <row r="445"/>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
@@ -48300,7 +48291,6 @@
         </is>
       </c>
     </row>
-    <row r="530"/>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
@@ -52358,7 +52348,6 @@
         </is>
       </c>
     </row>
-    <row r="622"/>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
@@ -52719,7 +52708,6 @@
         </is>
       </c>
     </row>
-    <row r="633"/>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
@@ -53324,7 +53312,6 @@
         </is>
       </c>
     </row>
-    <row r="651"/>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>

--- a/data/S1964_65_FINAL.xlsx
+++ b/data/S1964_65_FINAL.xlsx
@@ -18713,7 +18713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:N106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18775,6 +18775,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1964_65_FINAL.xlsx
+++ b/data/S1964_65_FINAL.xlsx
@@ -19059,6 +19059,16 @@
           <t>NODE_S1964_65_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1964_65_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19073,6 +19083,14 @@
         <is>
           <t>NODE_S1963_64_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -19106,6 +19124,8 @@
           <t>NODE_S1964_65_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19120,6 +19140,14 @@
         <is>
           <t>NODE_S1963_64_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -19153,6 +19181,8 @@
           <t>NODE_S1964_65_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19167,6 +19197,14 @@
         <is>
           <t>NODE_S1963_64_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>7.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -19895,6 +19933,8 @@
           <t>NODE_S1964_65_0020</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19909,6 +19949,14 @@
         <is>
           <t>NODE_S1963_64_0023</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -20743,6 +20791,8 @@
           <t>NODE_S1964_65_0039</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20752,6 +20802,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -21277,6 +21335,8 @@
           <t>NODE_S1964_65_0051</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21286,6 +21346,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="57">
@@ -21695,6 +21763,8 @@
           <t>NODE_S1964_65_0060</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21709,6 +21779,14 @@
         <is>
           <t>NODE_S1963_64_0062</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -22217,6 +22295,8 @@
           <t>NODE_S1964_65_0071</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22231,6 +22311,14 @@
         <is>
           <t>NODE_S1963_64_0073</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -22709,6 +22797,8 @@
           <t>NODE_S1964_65_0082</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22723,6 +22813,14 @@
         <is>
           <t>NODE_S1963_64_0085</t>
         </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="88">

--- a/data/S1964_65_FINAL.xlsx
+++ b/data/S1964_65_FINAL.xlsx
@@ -19124,8 +19124,6 @@
           <t>NODE_S1964_65_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19181,8 +19179,6 @@
           <t>NODE_S1964_65_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19933,8 +19929,6 @@
           <t>NODE_S1964_65_0020</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20791,8 +20785,6 @@
           <t>NODE_S1964_65_0039</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21335,8 +21327,6 @@
           <t>NODE_S1964_65_0051</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21763,8 +21753,6 @@
           <t>NODE_S1964_65_0060</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22295,8 +22283,6 @@
           <t>NODE_S1964_65_0071</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22797,8 +22783,6 @@
           <t>NODE_S1964_65_0082</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27459,6 +27443,10 @@
         </is>
       </c>
     </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
@@ -33408,6 +33396,7 @@
         </is>
       </c>
     </row>
+    <row r="192"/>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
@@ -36047,6 +36036,7 @@
         </is>
       </c>
     </row>
+    <row r="250"/>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
@@ -37958,6 +37948,7 @@
         </is>
       </c>
     </row>
+    <row r="294"/>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
@@ -40252,6 +40243,7 @@
         </is>
       </c>
     </row>
+    <row r="347"/>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
@@ -44691,6 +44683,7 @@
         </is>
       </c>
     </row>
+    <row r="445"/>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
@@ -48399,6 +48392,7 @@
         </is>
       </c>
     </row>
+    <row r="530"/>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
@@ -52456,6 +52450,7 @@
         </is>
       </c>
     </row>
+    <row r="622"/>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
@@ -52816,6 +52811,7 @@
         </is>
       </c>
     </row>
+    <row r="633"/>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
@@ -53420,6 +53416,7 @@
         </is>
       </c>
     </row>
+    <row r="651"/>
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
